--- a/logs/trivia_creative_writing/gpt-4o-mini_wo_sys_mes/accuracy_results_gpt-4o-mini_wo_sys_mes.xlsx
+++ b/logs/trivia_creative_writing/gpt-4o-mini_wo_sys_mes/accuracy_results_gpt-4o-mini_wo_sys_mes.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -481,7 +481,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -504,7 +504,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -527,7 +527,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -573,7 +573,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -596,7 +596,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -619,7 +619,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -665,7 +665,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -688,7 +688,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -711,7 +711,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -734,7 +734,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -757,7 +757,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -780,7 +780,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -803,7 +803,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -826,7 +826,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -849,7 +849,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -872,7 +872,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -895,7 +895,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -918,7 +918,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -941,7 +941,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -964,7 +964,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -987,7 +987,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1010,7 +1010,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1033,7 +1033,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1056,7 +1056,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1079,7 +1079,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1125,7 +1125,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1148,7 +1148,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1194,7 +1194,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1217,7 +1217,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1240,7 +1240,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1263,7 +1263,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1286,7 +1286,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1309,7 +1309,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1332,7 +1332,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1355,7 +1355,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1378,7 +1378,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1401,7 +1401,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1424,7 +1424,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1470,7 +1470,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1493,7 +1493,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1516,7 +1516,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1539,7 +1539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1562,7 +1562,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1585,7 +1585,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1608,7 +1608,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1631,7 +1631,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1654,7 +1654,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1677,7 +1677,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1700,7 +1700,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1723,7 +1723,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1746,7 +1746,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1769,7 +1769,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1792,7 +1792,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1815,7 +1815,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1838,7 +1838,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1861,7 +1861,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1884,7 +1884,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1907,7 +1907,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1930,7 +1930,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1953,7 +1953,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1976,7 +1976,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1999,7 +1999,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2022,7 +2022,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2068,7 +2068,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2091,7 +2091,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2114,7 +2114,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2137,7 +2137,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2160,7 +2160,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2183,7 +2183,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2206,7 +2206,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2229,7 +2229,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2252,7 +2252,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2275,7 +2275,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2298,7 +2298,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2321,7 +2321,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2344,7 +2344,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2367,7 +2367,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2390,7 +2390,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2413,7 +2413,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2436,7 +2436,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2459,7 +2459,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2482,7 +2482,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2505,7 +2505,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2528,7 +2528,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2551,7 +2551,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2574,7 +2574,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2597,7 +2597,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2620,7 +2620,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2643,7 +2643,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2666,7 +2666,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2689,7 +2689,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2712,7 +2712,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2735,7 +2735,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2758,7 +2758,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2783,7 +2783,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2806,7 +2806,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2829,7 +2829,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2852,7 +2852,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2875,7 +2875,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2898,7 +2898,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2921,7 +2921,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2944,7 +2944,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2967,7 +2967,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2990,7 +2990,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3013,7 +3013,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3036,7 +3036,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3059,7 +3059,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3082,7 +3082,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3105,7 +3105,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3128,7 +3128,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3151,7 +3151,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3174,7 +3174,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3197,7 +3197,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3220,7 +3220,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3243,7 +3243,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3266,7 +3266,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3289,7 +3289,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3312,7 +3312,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3335,7 +3335,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3358,7 +3358,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3381,7 +3381,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3404,7 +3404,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3427,7 +3427,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3450,7 +3450,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3473,7 +3473,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3496,7 +3496,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3519,7 +3519,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3542,7 +3542,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3565,7 +3565,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3588,7 +3588,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3611,7 +3611,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3634,7 +3634,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3657,7 +3657,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3680,7 +3680,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3703,7 +3703,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3726,7 +3726,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3749,7 +3749,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3772,7 +3772,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3795,7 +3795,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3818,7 +3818,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3841,7 +3841,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3864,7 +3864,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3887,7 +3887,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3910,7 +3910,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3933,7 +3933,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3956,7 +3956,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -3979,7 +3979,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4002,7 +4002,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4025,7 +4025,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4048,7 +4048,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4071,7 +4071,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4094,7 +4094,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4117,7 +4117,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4140,7 +4140,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4163,7 +4163,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4186,7 +4186,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4209,7 +4209,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4232,7 +4232,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4255,7 +4255,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4278,7 +4278,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4301,7 +4301,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4324,7 +4324,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4347,7 +4347,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4370,7 +4370,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4393,7 +4393,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4416,7 +4416,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4439,7 +4439,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4462,7 +4462,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4485,7 +4485,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4508,7 +4508,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4531,7 +4531,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4554,7 +4554,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4577,7 +4577,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4600,7 +4600,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4623,7 +4623,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4646,7 +4646,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4669,7 +4669,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4692,7 +4692,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4715,7 +4715,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4738,7 +4738,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4761,7 +4761,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4784,7 +4784,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4807,7 +4807,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4830,7 +4830,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4853,7 +4853,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4876,7 +4876,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4899,7 +4899,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4922,7 +4922,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4945,7 +4945,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4968,7 +4968,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4991,7 +4991,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -5014,7 +5014,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -5037,7 +5037,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5060,7 +5060,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5083,7 +5083,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5108,7 +5108,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5131,7 +5131,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5154,7 +5154,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5177,7 +5177,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -5200,7 +5200,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -5223,7 +5223,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -5246,7 +5246,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -5269,7 +5269,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -5292,7 +5292,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -5315,7 +5315,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -5338,7 +5338,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -5361,7 +5361,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5384,7 +5384,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5407,7 +5407,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5430,7 +5430,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5453,7 +5453,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5476,7 +5476,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5499,7 +5499,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5522,7 +5522,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -5545,7 +5545,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5568,7 +5568,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -5591,7 +5591,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5614,7 +5614,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5637,7 +5637,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -5660,7 +5660,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -5683,7 +5683,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5706,7 +5706,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -5729,7 +5729,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5752,7 +5752,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5775,7 +5775,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -5798,7 +5798,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -5821,7 +5821,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5844,7 +5844,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -5867,7 +5867,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -5890,7 +5890,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -5913,7 +5913,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -5936,7 +5936,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -5959,7 +5959,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -5982,7 +5982,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -6005,7 +6005,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -6028,7 +6028,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -6051,7 +6051,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -6074,7 +6074,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -6097,7 +6097,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -6120,7 +6120,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -6143,7 +6143,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -6166,7 +6166,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -6189,7 +6189,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -6212,7 +6212,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -6235,7 +6235,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -6258,7 +6258,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -6281,7 +6281,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -6304,7 +6304,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -6327,7 +6327,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -6350,7 +6350,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -6373,7 +6373,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -6396,7 +6396,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -6419,7 +6419,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -6442,7 +6442,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -6465,7 +6465,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -6488,7 +6488,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -6511,7 +6511,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -6534,7 +6534,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -6557,7 +6557,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -6580,7 +6580,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -6603,7 +6603,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -6626,7 +6626,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -6649,7 +6649,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -6672,7 +6672,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -6695,7 +6695,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -6718,7 +6718,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -6741,7 +6741,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -6764,7 +6764,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -6787,7 +6787,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -6810,7 +6810,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -6833,7 +6833,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -6856,7 +6856,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -6879,7 +6879,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -6902,7 +6902,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -6925,7 +6925,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -6948,7 +6948,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -6971,7 +6971,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -6994,7 +6994,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -7017,7 +7017,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -7040,7 +7040,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -7063,7 +7063,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -7086,7 +7086,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -7109,7 +7109,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -7132,7 +7132,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -7155,7 +7155,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -7178,7 +7178,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -7201,7 +7201,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -7224,7 +7224,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -7247,7 +7247,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -7270,7 +7270,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -7293,7 +7293,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -7316,7 +7316,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -7339,7 +7339,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -7362,7 +7362,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -7385,7 +7385,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -7408,7 +7408,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_10.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -7433,7 +7433,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -7456,7 +7456,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -7479,7 +7479,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -7502,7 +7502,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -7525,7 +7525,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -7548,7 +7548,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -7571,7 +7571,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -7594,7 +7594,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -7617,7 +7617,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -7640,7 +7640,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -7663,7 +7663,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -7686,7 +7686,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -7709,7 +7709,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -7732,7 +7732,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -7755,7 +7755,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -7778,7 +7778,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -7801,7 +7801,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -7824,7 +7824,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -7847,7 +7847,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -7870,7 +7870,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -7893,7 +7893,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -7916,7 +7916,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -7939,7 +7939,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -7962,7 +7962,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -7985,7 +7985,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -8008,7 +8008,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -8031,7 +8031,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -8054,7 +8054,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -8077,7 +8077,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -8100,7 +8100,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -8123,7 +8123,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -8146,7 +8146,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -8169,7 +8169,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -8192,7 +8192,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -8215,7 +8215,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -8238,7 +8238,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -8261,7 +8261,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -8284,7 +8284,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -8307,7 +8307,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -8330,7 +8330,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -8353,7 +8353,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -8376,7 +8376,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -8399,7 +8399,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -8422,7 +8422,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -8445,7 +8445,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -8468,7 +8468,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -8491,7 +8491,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -8514,7 +8514,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -8537,7 +8537,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -8560,7 +8560,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -8583,7 +8583,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -8606,7 +8606,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -8629,7 +8629,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -8652,7 +8652,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -8675,7 +8675,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -8698,7 +8698,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -8721,7 +8721,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -8744,7 +8744,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -8767,7 +8767,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -8790,7 +8790,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -8813,7 +8813,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -8836,7 +8836,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -8859,7 +8859,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -8882,7 +8882,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -8905,7 +8905,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -8928,7 +8928,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -8951,7 +8951,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -8974,7 +8974,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -8997,7 +8997,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -9020,7 +9020,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -9043,7 +9043,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -9066,7 +9066,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -9089,7 +9089,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -9112,7 +9112,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -9135,7 +9135,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -9158,7 +9158,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -9181,7 +9181,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -9204,7 +9204,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -9227,7 +9227,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -9250,7 +9250,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -9273,7 +9273,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -9296,7 +9296,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -9319,7 +9319,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -9342,7 +9342,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -9365,7 +9365,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -9388,7 +9388,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -9411,7 +9411,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -9434,7 +9434,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -9457,7 +9457,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -9480,7 +9480,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -9503,7 +9503,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -9526,7 +9526,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -9549,7 +9549,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -9572,7 +9572,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -9595,7 +9595,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -9618,7 +9618,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -9641,7 +9641,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -9664,7 +9664,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -9687,7 +9687,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -9710,7 +9710,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -9733,7 +9733,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-bpp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -9758,7 +9758,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -9781,7 +9781,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -9804,7 +9804,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -9827,7 +9827,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -9850,7 +9850,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -9873,7 +9873,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -9896,7 +9896,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -9919,7 +9919,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -9942,7 +9942,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -9965,7 +9965,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -9988,7 +9988,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -10011,7 +10011,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -10034,7 +10034,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -10057,7 +10057,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -10080,7 +10080,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -10103,7 +10103,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -10126,7 +10126,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -10149,7 +10149,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -10172,7 +10172,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -10195,7 +10195,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -10218,7 +10218,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -10241,7 +10241,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -10264,7 +10264,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -10287,7 +10287,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -10310,7 +10310,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -10356,7 +10356,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -10379,7 +10379,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -10402,7 +10402,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -10425,7 +10425,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -10448,7 +10448,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -10471,7 +10471,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -10494,7 +10494,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -10517,7 +10517,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -10540,7 +10540,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -10563,7 +10563,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -10586,7 +10586,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -10609,7 +10609,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -10632,7 +10632,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -10655,7 +10655,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -10678,7 +10678,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -10701,7 +10701,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -10724,7 +10724,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -10747,7 +10747,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -10770,7 +10770,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -10793,7 +10793,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -10816,7 +10816,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -10839,7 +10839,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -10862,7 +10862,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -10885,7 +10885,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -10908,7 +10908,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -10931,7 +10931,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -10954,7 +10954,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -10977,7 +10977,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -11000,7 +11000,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -11023,7 +11023,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -11046,7 +11046,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -11069,7 +11069,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -11092,7 +11092,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -11115,7 +11115,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -11138,7 +11138,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -11161,7 +11161,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -11184,7 +11184,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -11207,7 +11207,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -11230,7 +11230,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -11253,7 +11253,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -11276,7 +11276,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -11299,7 +11299,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -11322,7 +11322,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -11345,7 +11345,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -11368,7 +11368,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -11391,7 +11391,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -11414,7 +11414,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -11437,7 +11437,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -11460,7 +11460,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -11483,7 +11483,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -11506,7 +11506,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -11529,7 +11529,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -11552,7 +11552,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -11575,7 +11575,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -11598,7 +11598,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -11621,7 +11621,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -11644,7 +11644,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -11667,7 +11667,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -11690,7 +11690,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -11713,7 +11713,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -11736,7 +11736,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -11759,7 +11759,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -11782,7 +11782,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -11805,7 +11805,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -11828,7 +11828,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -11851,7 +11851,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -11874,7 +11874,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -11897,7 +11897,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -11920,7 +11920,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -11943,7 +11943,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -11966,7 +11966,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -11989,7 +11989,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -12012,7 +12012,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -12035,7 +12035,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -12058,7 +12058,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-spp_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -12083,7 +12083,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -12106,7 +12106,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -12129,7 +12129,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -12152,7 +12152,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -12175,7 +12175,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -12198,7 +12198,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -12221,7 +12221,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -12244,7 +12244,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -12267,7 +12267,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -12290,7 +12290,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -12313,7 +12313,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -12336,7 +12336,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -12359,7 +12359,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -12382,7 +12382,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -12405,7 +12405,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -12428,7 +12428,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -12451,7 +12451,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -12474,7 +12474,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -12497,7 +12497,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -12520,7 +12520,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -12543,7 +12543,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -12566,7 +12566,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -12589,7 +12589,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -12612,7 +12612,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -12635,7 +12635,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -12658,7 +12658,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -12681,7 +12681,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -12704,7 +12704,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -12727,7 +12727,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -12750,7 +12750,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -12773,7 +12773,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -12796,7 +12796,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -12819,7 +12819,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -12842,7 +12842,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -12865,7 +12865,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -12888,7 +12888,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -12911,7 +12911,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -12934,7 +12934,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -12957,7 +12957,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -12980,7 +12980,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -13003,7 +13003,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -13026,7 +13026,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -13049,7 +13049,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -13072,7 +13072,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -13095,7 +13095,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -13118,7 +13118,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -13141,7 +13141,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -13164,7 +13164,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -13187,7 +13187,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -13210,7 +13210,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -13233,7 +13233,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -13256,7 +13256,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -13279,7 +13279,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -13302,7 +13302,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -13325,7 +13325,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -13348,7 +13348,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -13371,7 +13371,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -13394,7 +13394,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -13417,7 +13417,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -13440,7 +13440,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -13463,7 +13463,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -13486,7 +13486,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -13509,7 +13509,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -13532,7 +13532,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -13555,7 +13555,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -13578,7 +13578,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -13601,7 +13601,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -13624,7 +13624,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -13647,7 +13647,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -13670,7 +13670,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -13693,7 +13693,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -13716,7 +13716,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -13739,7 +13739,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -13762,7 +13762,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -13785,7 +13785,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -13808,7 +13808,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -13831,7 +13831,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -13854,7 +13854,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -13877,7 +13877,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
@@ -13900,7 +13900,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
@@ -13923,7 +13923,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
@@ -13946,7 +13946,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
@@ -13969,7 +13969,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
@@ -13992,7 +13992,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
@@ -14015,7 +14015,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
@@ -14038,7 +14038,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
@@ -14061,7 +14061,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
@@ -14084,7 +14084,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
@@ -14107,7 +14107,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
@@ -14130,7 +14130,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
@@ -14153,7 +14153,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
@@ -14176,7 +14176,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
@@ -14199,7 +14199,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
@@ -14222,7 +14222,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
@@ -14245,7 +14245,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
@@ -14268,7 +14268,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
@@ -14291,7 +14291,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
@@ -14314,7 +14314,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
@@ -14337,7 +14337,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
@@ -14360,7 +14360,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
@@ -14383,7 +14383,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100__wo_sys.jsonl</t>
+          <t>trivia_creative_writing_100_n_5.jsonl__method-standard_model-gpt-4o-mini_temp-_temp-0.0_topp-_topp-1.0_start0-end100_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
